--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -808,772 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.7887,0.1087,0.0301,0.0587</t>
-  </si>
-  <si>
-    <t>0.0044,0.0042,0.0004,0.9978</t>
-  </si>
-  <si>
-    <t>0.0498,0.0778,0.0110,0.9609</t>
-  </si>
-  <si>
-    <t>0.0149,0.0228,0.0033,0.9903</t>
-  </si>
-  <si>
-    <t>0.9850,0.0119,0.0016,0.0018</t>
-  </si>
-  <si>
-    <t>0.9768,0.0202,0.0021,0.0036</t>
-  </si>
-  <si>
-    <t>0.9767,0.0188,0.0021,0.0026</t>
-  </si>
-  <si>
-    <t>0.9827,0.0079,0.0018,0.0040</t>
-  </si>
-  <si>
-    <t>0.9859,0.0122,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9798,0.0172,0.0008,0.0031</t>
-  </si>
-  <si>
-    <t>0.9873,0.0130,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9814,0.0152,0.0018,0.0027</t>
-  </si>
-  <si>
-    <t>0.5887,0.1082,0.3389,0.0344</t>
-  </si>
-  <si>
-    <t>0.4425,0.0884,0.4948,0.0225</t>
-  </si>
-  <si>
-    <t>0.4289,0.1546,0.4718,0.0238</t>
-  </si>
-  <si>
-    <t>0.3593,0.1677,0.5227,0.0258</t>
-  </si>
-  <si>
-    <t>0.5147,0.0642,0.4446,0.0452</t>
-  </si>
-  <si>
-    <t>0.1139,0.9248,0.0128,0.0003</t>
-  </si>
-  <si>
-    <t>0.1390,0.9027,0.0079,0.0010</t>
-  </si>
-  <si>
-    <t>0.6928,0.3768,0.0230,0.0046</t>
-  </si>
-  <si>
-    <t>0.1771,0.8650,0.0064,0.0037</t>
-  </si>
-  <si>
-    <t>0.1826,0.8913,0.0023,0.0005</t>
-  </si>
-  <si>
-    <t>0.5258,0.0549,0.3430,0.1061</t>
-  </si>
-  <si>
-    <t>0.3216,0.0645,0.4005,0.2877</t>
-  </si>
-  <si>
-    <t>0.1701,0.0093,0.8740,0.0096</t>
-  </si>
-  <si>
-    <t>0.3089,0.0183,0.7390,0.0126</t>
-  </si>
-  <si>
-    <t>0.1931,0.0085,0.8746,0.0075</t>
-  </si>
-  <si>
-    <t>0.2557,0.1285,0.2812,0.4914</t>
-  </si>
-  <si>
-    <t>0.0402,0.0065,0.9697,0.0032</t>
-  </si>
-  <si>
-    <t>0.6353,0.3561,0.0608,0.0087</t>
-  </si>
-  <si>
-    <t>0.6702,0.1410,0.2039,0.0218</t>
-  </si>
-  <si>
-    <t>0.0144,0.0232,0.9722,0.0092</t>
-  </si>
-  <si>
-    <t>0.0524,0.7707,0.3316,0.0015</t>
-  </si>
-  <si>
-    <t>0.6682,0.3040,0.0458,0.0427</t>
-  </si>
-  <si>
-    <t>0.7417,0.2443,0.0336,0.0312</t>
-  </si>
-  <si>
-    <t>0.7767,0.3267,0.0102,0.0023</t>
-  </si>
-  <si>
-    <t>0.1352,0.8507,0.1153,0.0106</t>
-  </si>
-  <si>
-    <t>0.0308,0.8861,0.3153,0.0074</t>
-  </si>
-  <si>
-    <t>0.0139,0.4687,0.8929,0.0022</t>
-  </si>
-  <si>
-    <t>0.0598,0.4024,0.7338,0.0072</t>
-  </si>
-  <si>
-    <t>0.1049,0.1494,0.8058,0.0196</t>
-  </si>
-  <si>
-    <t>0.1325,0.1170,0.7764,0.0107</t>
-  </si>
-  <si>
-    <t>0.0125,0.9615,0.1375,0.0007</t>
-  </si>
-  <si>
-    <t>0.1912,0.0472,0.8054,0.0100</t>
-  </si>
-  <si>
-    <t>0.0563,0.5443,0.0161,0.8189</t>
-  </si>
-  <si>
-    <t>0.0061,0.9719,0.0113,0.0423</t>
-  </si>
-  <si>
-    <t>0.0110,0.9714,0.0480,0.0056</t>
-  </si>
-  <si>
-    <t>0.0108,0.9750,0.0325,0.0046</t>
-  </si>
-  <si>
-    <t>0.0271,0.6597,0.7565,0.0105</t>
-  </si>
-  <si>
-    <t>0.0066,0.5345,0.9152,0.0017</t>
-  </si>
-  <si>
-    <t>0.2104,0.0106,0.8502,0.0034</t>
-  </si>
-  <si>
-    <t>0.1091,0.0054,0.9200,0.0120</t>
-  </si>
-  <si>
-    <t>0.2029,0.0944,0.7318,0.0193</t>
-  </si>
-  <si>
-    <t>0.0081,0.5672,0.8845,0.0015</t>
-  </si>
-  <si>
-    <t>0.9760,0.0258,0.0023,0.0027</t>
-  </si>
-  <si>
-    <t>0.9531,0.0456,0.0076,0.0054</t>
-  </si>
-  <si>
-    <t>0.9096,0.1212,0.0048,0.0039</t>
-  </si>
-  <si>
-    <t>0.0851,0.1637,0.8476,0.0115</t>
-  </si>
-  <si>
-    <t>0.9693,0.0106,0.0034,0.0117</t>
-  </si>
-  <si>
-    <t>0.9787,0.0167,0.0018,0.0033</t>
-  </si>
-  <si>
-    <t>0.9750,0.0277,0.0021,0.0019</t>
-  </si>
-  <si>
-    <t>0.0070,0.9408,0.4082,0.0011</t>
-  </si>
-  <si>
-    <t>0.0449,0.1274,0.9075,0.0060</t>
-  </si>
-  <si>
-    <t>0.2020,0.2242,0.6194,0.1256</t>
-  </si>
-  <si>
-    <t>0.0068,0.8927,0.7010,0.0022</t>
-  </si>
-  <si>
-    <t>0.0163,0.1104,0.9540,0.0030</t>
-  </si>
-  <si>
-    <t>0.0994,0.8273,0.1163,0.0305</t>
-  </si>
-  <si>
-    <t>0.0125,0.9882,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.3552,0.0314,0.7078,0.0206</t>
-  </si>
-  <si>
-    <t>0.4956,0.4731,0.1219,0.0199</t>
-  </si>
-  <si>
-    <t>0.0643,0.2836,0.7292,0.0427</t>
-  </si>
-  <si>
-    <t>0.0078,0.9470,0.3235,0.0010</t>
-  </si>
-  <si>
-    <t>0.0163,0.8178,0.5327,0.0011</t>
-  </si>
-  <si>
-    <t>0.0046,0.9585,0.2959,0.0009</t>
-  </si>
-  <si>
-    <t>0.0022,0.9678,0.4730,0.0004</t>
-  </si>
-  <si>
-    <t>0.0112,0.0472,0.0453,0.9748</t>
-  </si>
-  <si>
-    <t>0.0017,0.0063,0.0012,0.9982</t>
-  </si>
-  <si>
-    <t>0.0056,0.0047,0.0078,0.9931</t>
-  </si>
-  <si>
-    <t>0.0019,0.0356,0.0009,0.9980</t>
-  </si>
-  <si>
-    <t>0.0027,0.0205,0.0072,0.9952</t>
-  </si>
-  <si>
-    <t>0.0020,0.0214,0.0007,0.9982</t>
-  </si>
-  <si>
-    <t>0.0061,0.9148,0.5763,0.0011</t>
-  </si>
-  <si>
-    <t>0.0025,0.8642,0.8544,0.0004</t>
-  </si>
-  <si>
-    <t>0.0190,0.8420,0.5466,0.0032</t>
-  </si>
-  <si>
-    <t>0.0126,0.7204,0.7532,0.0024</t>
-  </si>
-  <si>
-    <t>0.0014,0.9650,0.5153,0.0002</t>
-  </si>
-  <si>
-    <t>0.0039,0.8825,0.7305,0.0007</t>
-  </si>
-  <si>
-    <t>0.9849,0.0120,0.0013,0.0017</t>
-  </si>
-  <si>
-    <t>0.9684,0.0312,0.0033,0.0043</t>
-  </si>
-  <si>
-    <t>0.9798,0.0134,0.0018,0.0035</t>
-  </si>
-  <si>
-    <t>0.9785,0.0121,0.0013,0.0059</t>
-  </si>
-  <si>
-    <t>0.9716,0.0253,0.0031,0.0040</t>
-  </si>
-  <si>
-    <t>0.9884,0.0054,0.0005,0.0028</t>
-  </si>
-  <si>
-    <t>0.9806,0.0158,0.0010,0.0033</t>
-  </si>
-  <si>
-    <t>0.9837,0.0117,0.0015,0.0029</t>
-  </si>
-  <si>
-    <t>0.9867,0.0089,0.0005,0.0028</t>
-  </si>
-  <si>
-    <t>0.9772,0.0145,0.0024,0.0048</t>
-  </si>
-  <si>
-    <t>0.9849,0.0074,0.0008,0.0044</t>
-  </si>
-  <si>
-    <t>0.9705,0.0106,0.0017,0.0122</t>
-  </si>
-  <si>
-    <t>0.9876,0.0081,0.0007,0.0020</t>
-  </si>
-  <si>
-    <t>0.9755,0.0265,0.0025,0.0023</t>
-  </si>
-  <si>
-    <t>0.9883,0.0099,0.0005,0.0015</t>
-  </si>
-  <si>
-    <t>0.9865,0.0137,0.0008,0.0013</t>
-  </si>
-  <si>
-    <t>0.0065,0.0046,0.9851,0.0053</t>
-  </si>
-  <si>
-    <t>0.3000,0.0638,0.6584,0.0112</t>
-  </si>
-  <si>
-    <t>0.3954,0.0488,0.5593,0.0765</t>
-  </si>
-  <si>
-    <t>0.2803,0.0232,0.7484,0.0064</t>
-  </si>
-  <si>
-    <t>0.4548,0.7293,0.0044,0.0009</t>
-  </si>
-  <si>
-    <t>0.6438,0.4859,0.0140,0.0014</t>
-  </si>
-  <si>
-    <t>0.5554,0.6097,0.0058,0.0015</t>
-  </si>
-  <si>
-    <t>0.4449,0.6944,0.0060,0.0023</t>
-  </si>
-  <si>
-    <t>0.1541,0.8895,0.0056,0.0014</t>
-  </si>
-  <si>
-    <t>0.0363,0.9690,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.7831,0.2842,0.0192,0.0017</t>
-  </si>
-  <si>
-    <t>0.5569,0.2465,0.1654,0.1983</t>
-  </si>
-  <si>
-    <t>0.5304,0.0340,0.4879,0.0163</t>
-  </si>
-  <si>
-    <t>0.4554,0.2861,0.1958,0.2202</t>
-  </si>
-  <si>
-    <t>0.1771,0.1118,0.7380,0.0039</t>
-  </si>
-  <si>
-    <t>0.1335,0.0618,0.0302,0.8900</t>
-  </si>
-  <si>
-    <t>0.0060,0.9882,0.0284,0.0005</t>
-  </si>
-  <si>
-    <t>0.0043,0.9882,0.0319,0.0015</t>
-  </si>
-  <si>
-    <t>0.0148,0.9418,0.0213,0.0871</t>
-  </si>
-  <si>
-    <t>0.0056,0.9774,0.2132,0.0005</t>
-  </si>
-  <si>
-    <t>0.0654,0.9376,0.0310,0.0004</t>
-  </si>
-  <si>
-    <t>0.8542,0.1468,0.0333,0.0044</t>
-  </si>
-  <si>
-    <t>0.6502,0.4291,0.0238,0.0077</t>
-  </si>
-  <si>
-    <t>0.8058,0.2016,0.0362,0.0073</t>
-  </si>
-  <si>
-    <t>0.9260,0.0173,0.0085,0.0457</t>
-  </si>
-  <si>
-    <t>0.9566,0.0279,0.0059,0.0083</t>
-  </si>
-  <si>
-    <t>0.9088,0.0455,0.0135,0.0288</t>
-  </si>
-  <si>
-    <t>0.9692,0.0189,0.0026,0.0086</t>
-  </si>
-  <si>
-    <t>0.9377,0.0339,0.0215,0.0101</t>
-  </si>
-  <si>
-    <t>0.9592,0.0267,0.0116,0.0046</t>
-  </si>
-  <si>
-    <t>0.9637,0.0223,0.0022,0.0107</t>
-  </si>
-  <si>
-    <t>0.0129,0.6915,0.8097,0.0028</t>
-  </si>
-  <si>
-    <t>0.0359,0.7781,0.4489,0.0034</t>
-  </si>
-  <si>
-    <t>0.0128,0.5910,0.8244,0.0021</t>
-  </si>
-  <si>
-    <t>0.0631,0.1878,0.8113,0.0046</t>
-  </si>
-  <si>
-    <t>0.3044,0.1335,0.1964,0.5581</t>
-  </si>
-  <si>
-    <t>0.5565,0.1895,0.2465,0.0992</t>
-  </si>
-  <si>
-    <t>0.4124,0.0186,0.6332,0.0315</t>
-  </si>
-  <si>
-    <t>0.5923,0.1918,0.2747,0.0300</t>
-  </si>
-  <si>
-    <t>0.0073,0.0157,0.0047,0.9932</t>
-  </si>
-  <si>
-    <t>0.0010,0.0057,0.0003,0.9991</t>
-  </si>
-  <si>
-    <t>0.0048,0.0167,0.0080,0.9935</t>
-  </si>
-  <si>
-    <t>0.0111,0.0370,0.0037,0.9912</t>
-  </si>
-  <si>
-    <t>0.0092,0.9158,0.5218,0.0018</t>
-  </si>
-  <si>
-    <t>0.9253,0.0328,0.0017,0.0254</t>
-  </si>
-  <si>
-    <t>0.3275,0.6941,0.0110,0.0149</t>
-  </si>
-  <si>
-    <t>0.9543,0.0261,0.0026,0.0139</t>
-  </si>
-  <si>
-    <t>0.8321,0.1802,0.0294,0.0185</t>
-  </si>
-  <si>
-    <t>0.9010,0.0323,0.0063,0.0502</t>
-  </si>
-  <si>
-    <t>0.3807,0.1622,0.0274,0.6529</t>
-  </si>
-  <si>
-    <t>0.9761,0.0086,0.0015,0.0073</t>
-  </si>
-  <si>
-    <t>0.0361,0.3835,0.8416,0.0292</t>
-  </si>
-  <si>
-    <t>0.2090,0.0051,0.0130,0.8562</t>
-  </si>
-  <si>
-    <t>0.8650,0.0304,0.0476,0.0413</t>
-  </si>
-  <si>
-    <t>0.2490,0.7031,0.0192,0.0706</t>
-  </si>
-  <si>
-    <t>0.6974,0.2163,0.0240,0.0721</t>
-  </si>
-  <si>
-    <t>0.8315,0.0996,0.0728,0.0156</t>
-  </si>
-  <si>
-    <t>0.2333,0.5135,0.0483,0.4180</t>
-  </si>
-  <si>
-    <t>0.5836,0.4432,0.0258,0.0078</t>
-  </si>
-  <si>
-    <t>0.3844,0.5949,0.0785,0.0260</t>
-  </si>
-  <si>
-    <t>0.9647,0.0135,0.0026,0.0129</t>
-  </si>
-  <si>
-    <t>0.9405,0.0082,0.0005,0.0492</t>
-  </si>
-  <si>
-    <t>0.9745,0.0123,0.0016,0.0065</t>
-  </si>
-  <si>
-    <t>0.9795,0.0120,0.0020,0.0035</t>
-  </si>
-  <si>
-    <t>0.9708,0.0260,0.0027,0.0025</t>
-  </si>
-  <si>
-    <t>0.9369,0.0532,0.0143,0.0059</t>
-  </si>
-  <si>
-    <t>0.9419,0.0166,0.0033,0.0317</t>
-  </si>
-  <si>
-    <t>0.9594,0.0122,0.0016,0.0190</t>
-  </si>
-  <si>
-    <t>0.1751,0.8516,0.0186,0.0049</t>
-  </si>
-  <si>
-    <t>0.7695,0.3551,0.0108,0.0016</t>
-  </si>
-  <si>
-    <t>0.7653,0.3684,0.0094,0.0020</t>
-  </si>
-  <si>
-    <t>0.9176,0.0349,0.0228,0.0146</t>
-  </si>
-  <si>
-    <t>0.9386,0.0632,0.0089,0.0032</t>
-  </si>
-  <si>
-    <t>0.9053,0.0798,0.0071,0.0164</t>
-  </si>
-  <si>
-    <t>0.9357,0.0839,0.0076,0.0022</t>
-  </si>
-  <si>
-    <t>0.8610,0.2903,0.0017,0.0007</t>
-  </si>
-  <si>
-    <t>0.0486,0.0113,0.9532,0.0163</t>
-  </si>
-  <si>
-    <t>0.9164,0.0659,0.0191,0.0089</t>
-  </si>
-  <si>
-    <t>0.0791,0.0291,0.9207,0.0059</t>
-  </si>
-  <si>
-    <t>0.0295,0.4072,0.8354,0.0033</t>
-  </si>
-  <si>
-    <t>0.1689,0.0116,0.8744,0.0118</t>
-  </si>
-  <si>
-    <t>0.0408,0.7248,0.4922,0.0056</t>
-  </si>
-  <si>
-    <t>0.0835,0.0115,0.9334,0.0060</t>
-  </si>
-  <si>
-    <t>0.0735,0.0014,0.9638,0.0020</t>
-  </si>
-  <si>
-    <t>0.0399,0.0219,0.9559,0.0020</t>
-  </si>
-  <si>
-    <t>0.4112,0.0346,0.2970,0.2492</t>
-  </si>
-  <si>
-    <t>0.3963,0.0198,0.6858,0.0049</t>
-  </si>
-  <si>
-    <t>0.6095,0.1124,0.3094,0.0087</t>
-  </si>
-  <si>
-    <t>0.5347,0.2143,0.3016,0.0280</t>
-  </si>
-  <si>
-    <t>0.1473,0.7392,0.1921,0.0107</t>
-  </si>
-  <si>
-    <t>0.3624,0.4785,0.2265,0.0236</t>
-  </si>
-  <si>
-    <t>0.4737,0.0206,0.5646,0.0143</t>
-  </si>
-  <si>
-    <t>0.4660,0.0543,0.5164,0.0205</t>
-  </si>
-  <si>
-    <t>0.8752,0.2167,0.0061,0.0027</t>
-  </si>
-  <si>
-    <t>0.8748,0.1969,0.0049,0.0028</t>
-  </si>
-  <si>
-    <t>0.8778,0.2296,0.0024,0.0020</t>
-  </si>
-  <si>
-    <t>0.9427,0.0553,0.0084,0.0080</t>
-  </si>
-  <si>
-    <t>0.9326,0.0872,0.0066,0.0033</t>
-  </si>
-  <si>
-    <t>0.2979,0.4057,0.3812,0.0202</t>
-  </si>
-  <si>
-    <t>0.5987,0.1514,0.2034,0.1084</t>
-  </si>
-  <si>
-    <t>0.3635,0.0703,0.0764,0.5508</t>
-  </si>
-  <si>
-    <t>0.4851,0.0515,0.4932,0.0212</t>
-  </si>
-  <si>
-    <t>0.6286,0.1349,0.1313,0.1213</t>
-  </si>
-  <si>
-    <t>0.3003,0.2913,0.3688,0.2439</t>
-  </si>
-  <si>
-    <t>0.0938,0.2514,0.7346,0.0151</t>
-  </si>
-  <si>
-    <t>0.0786,0.2660,0.8091,0.0195</t>
-  </si>
-  <si>
-    <t>0.0589,0.5071,0.7138,0.0250</t>
-  </si>
-  <si>
-    <t>0.0600,0.2965,0.7389,0.0065</t>
-  </si>
-  <si>
-    <t>0.9639,0.0335,0.0018,0.0050</t>
-  </si>
-  <si>
-    <t>0.9757,0.0123,0.0015,0.0064</t>
-  </si>
-  <si>
-    <t>0.9895,0.0057,0.0005,0.0022</t>
-  </si>
-  <si>
-    <t>0.9747,0.0262,0.0029,0.0017</t>
-  </si>
-  <si>
-    <t>0.9723,0.0218,0.0025,0.0055</t>
-  </si>
-  <si>
-    <t>0.9714,0.0272,0.0036,0.0014</t>
-  </si>
-  <si>
-    <t>0.9850,0.0172,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.9780,0.0215,0.0018,0.0019</t>
-  </si>
-  <si>
-    <t>0.2389,0.0299,0.7852,0.0179</t>
-  </si>
-  <si>
-    <t>0.5510,0.1530,0.3554,0.0355</t>
-  </si>
-  <si>
-    <t>0.6323,0.0632,0.1569,0.1434</t>
-  </si>
-  <si>
-    <t>0.0588,0.0216,0.9373,0.0012</t>
-  </si>
-  <si>
-    <t>0.0444,0.0187,0.9457,0.0108</t>
-  </si>
-  <si>
-    <t>0.0548,0.1429,0.8791,0.0030</t>
-  </si>
-  <si>
-    <t>0.0140,0.0136,0.9841,0.0016</t>
-  </si>
-  <si>
-    <t>0.2435,0.0375,0.7627,0.0079</t>
-  </si>
-  <si>
-    <t>0.0212,0.5952,0.7359,0.0023</t>
-  </si>
-  <si>
-    <t>0.1525,0.0621,0.8078,0.0208</t>
-  </si>
-  <si>
-    <t>0.4740,0.1721,0.2937,0.2140</t>
-  </si>
-  <si>
-    <t>0.6386,0.0662,0.3065,0.0167</t>
-  </si>
-  <si>
-    <t>0.4989,0.0422,0.4730,0.0508</t>
-  </si>
-  <si>
-    <t>0.5279,0.0292,0.4817,0.0288</t>
-  </si>
-  <si>
-    <t>0.9682,0.0293,0.0036,0.0037</t>
-  </si>
-  <si>
-    <t>0.9808,0.0187,0.0013,0.0017</t>
-  </si>
-  <si>
-    <t>0.9746,0.0206,0.0014,0.0038</t>
-  </si>
-  <si>
-    <t>0.9586,0.0404,0.0070,0.0039</t>
-  </si>
-  <si>
-    <t>0.9635,0.0149,0.0009,0.0133</t>
-  </si>
-  <si>
-    <t>0.9830,0.0170,0.0013,0.0017</t>
-  </si>
-  <si>
-    <t>0.9885,0.0108,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.9738,0.0230,0.0031,0.0035</t>
-  </si>
-  <si>
-    <t>0.0985,0.0909,0.8422,0.0033</t>
-  </si>
-  <si>
-    <t>0.0128,0.0937,0.9596,0.0015</t>
-  </si>
-  <si>
-    <t>0.0323,0.6306,0.6444,0.0045</t>
-  </si>
-  <si>
-    <t>0.3691,0.1089,0.5418,0.0592</t>
-  </si>
-  <si>
-    <t>0.1489,0.0164,0.8700,0.0141</t>
-  </si>
-  <si>
-    <t>0.2483,0.1160,0.6411,0.1444</t>
-  </si>
-  <si>
-    <t>0.3455,0.0586,0.2969,0.3425</t>
-  </si>
-  <si>
-    <t>0.1075,0.1474,0.8060,0.0416</t>
-  </si>
-  <si>
-    <t>0.3593,0.0115,0.0353,0.6496</t>
-  </si>
-  <si>
-    <t>0.0099,0.0699,0.0076,0.9885</t>
-  </si>
-  <si>
-    <t>0.0074,0.0024,0.0035,0.9943</t>
-  </si>
-  <si>
-    <t>0.0035,0.0030,0.0030,0.9963</t>
-  </si>
-  <si>
-    <t>0.0042,0.0012,0.0009,0.9975</t>
-  </si>
-  <si>
-    <t>0.1784,0.1846,0.0249,0.8432</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.5079,0.0510,0.0746,0.4194</t>
+  </si>
+  <si>
+    <t>0.0056,0.0069,0.0035,0.9953</t>
+  </si>
+  <si>
+    <t>0.0514,0.0243,0.0079,0.9683</t>
+  </si>
+  <si>
+    <t>0.0351,0.0256,0.0138,0.9738</t>
+  </si>
+  <si>
+    <t>0.9884,0.0065,0.0004,0.0027</t>
+  </si>
+  <si>
+    <t>0.9785,0.0132,0.0009,0.0043</t>
+  </si>
+  <si>
+    <t>0.9643,0.0326,0.0046,0.0043</t>
+  </si>
+  <si>
+    <t>0.9871,0.0087,0.0007,0.0018</t>
+  </si>
+  <si>
+    <t>0.9857,0.0127,0.0009,0.0018</t>
+  </si>
+  <si>
+    <t>0.9859,0.0151,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.9855,0.0137,0.0012,0.0015</t>
+  </si>
+  <si>
+    <t>0.9792,0.0206,0.0025,0.0019</t>
+  </si>
+  <si>
+    <t>0.5597,0.1852,0.3131,0.0541</t>
+  </si>
+  <si>
+    <t>0.5450,0.1160,0.3714,0.0589</t>
+  </si>
+  <si>
+    <t>0.6334,0.1065,0.2626,0.0331</t>
+  </si>
+  <si>
+    <t>0.2777,0.0383,0.7194,0.0176</t>
+  </si>
+  <si>
+    <t>0.5150,0.2816,0.2150,0.0900</t>
+  </si>
+  <si>
+    <t>0.0390,0.9674,0.0046,0.0007</t>
+  </si>
+  <si>
+    <t>0.1596,0.8713,0.0226,0.0004</t>
+  </si>
+  <si>
+    <t>0.6019,0.4838,0.0077,0.0093</t>
+  </si>
+  <si>
+    <t>0.1730,0.8868,0.0062,0.0013</t>
+  </si>
+  <si>
+    <t>0.0770,0.9423,0.0054,0.0005</t>
+  </si>
+  <si>
+    <t>0.4891,0.0366,0.4765,0.0525</t>
+  </si>
+  <si>
+    <t>0.5334,0.0730,0.2459,0.1821</t>
+  </si>
+  <si>
+    <t>0.1810,0.0112,0.8749,0.0055</t>
+  </si>
+  <si>
+    <t>0.4619,0.0147,0.5699,0.0354</t>
+  </si>
+  <si>
+    <t>0.2313,0.0083,0.8356,0.0135</t>
+  </si>
+  <si>
+    <t>0.3668,0.0102,0.6907,0.0152</t>
+  </si>
+  <si>
+    <t>0.0670,0.0068,0.9422,0.0098</t>
+  </si>
+  <si>
+    <t>0.5670,0.4872,0.0342,0.0022</t>
+  </si>
+  <si>
+    <t>0.3815,0.5632,0.0925,0.0344</t>
+  </si>
+  <si>
+    <t>0.0166,0.0639,0.9517,0.0189</t>
+  </si>
+  <si>
+    <t>0.1130,0.7053,0.3734,0.0084</t>
+  </si>
+  <si>
+    <t>0.7201,0.1999,0.0261,0.0728</t>
+  </si>
+  <si>
+    <t>0.5690,0.3507,0.1152,0.0243</t>
+  </si>
+  <si>
+    <t>0.7090,0.3625,0.0251,0.0021</t>
+  </si>
+  <si>
+    <t>0.0769,0.8591,0.2674,0.0077</t>
+  </si>
+  <si>
+    <t>0.0482,0.7050,0.5801,0.0147</t>
+  </si>
+  <si>
+    <t>0.0682,0.4488,0.7479,0.0152</t>
+  </si>
+  <si>
+    <t>0.0400,0.5795,0.7409,0.0073</t>
+  </si>
+  <si>
+    <t>0.2964,0.1133,0.6246,0.0652</t>
+  </si>
+  <si>
+    <t>0.0434,0.1409,0.9099,0.0041</t>
+  </si>
+  <si>
+    <t>0.0232,0.9441,0.1156,0.0024</t>
+  </si>
+  <si>
+    <t>0.0477,0.0705,0.9213,0.0050</t>
+  </si>
+  <si>
+    <t>0.0154,0.4850,0.0184,0.9334</t>
+  </si>
+  <si>
+    <t>0.0152,0.9683,0.0151,0.0088</t>
+  </si>
+  <si>
+    <t>0.0188,0.9681,0.0582,0.0009</t>
+  </si>
+  <si>
+    <t>0.0076,0.9840,0.0462,0.0010</t>
+  </si>
+  <si>
+    <t>0.0254,0.5149,0.8351,0.0030</t>
+  </si>
+  <si>
+    <t>0.0100,0.6231,0.8590,0.0014</t>
+  </si>
+  <si>
+    <t>0.3114,0.0403,0.6965,0.0105</t>
+  </si>
+  <si>
+    <t>0.2674,0.0038,0.8314,0.0095</t>
+  </si>
+  <si>
+    <t>0.0706,0.0067,0.9505,0.0028</t>
+  </si>
+  <si>
+    <t>0.0410,0.1099,0.9158,0.0067</t>
+  </si>
+  <si>
+    <t>0.9537,0.0758,0.0022,0.0016</t>
+  </si>
+  <si>
+    <t>0.9786,0.0132,0.0026,0.0047</t>
+  </si>
+  <si>
+    <t>0.9737,0.0240,0.0031,0.0017</t>
+  </si>
+  <si>
+    <t>0.0059,0.7783,0.8005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9389,0.0700,0.0090,0.0038</t>
+  </si>
+  <si>
+    <t>0.9862,0.0122,0.0010,0.0015</t>
+  </si>
+  <si>
+    <t>0.9344,0.0597,0.0065,0.0091</t>
+  </si>
+  <si>
+    <t>0.0108,0.8705,0.5819,0.0026</t>
+  </si>
+  <si>
+    <t>0.0431,0.2141,0.8684,0.0073</t>
+  </si>
+  <si>
+    <t>0.0477,0.2769,0.7967,0.0058</t>
+  </si>
+  <si>
+    <t>0.0123,0.7999,0.7132,0.0023</t>
+  </si>
+  <si>
+    <t>0.0322,0.0582,0.9464,0.0012</t>
+  </si>
+  <si>
+    <t>0.0686,0.9127,0.0455,0.0025</t>
+  </si>
+  <si>
+    <t>0.0098,0.9884,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.4667,0.1156,0.4866,0.0274</t>
+  </si>
+  <si>
+    <t>0.2235,0.7581,0.0172,0.0284</t>
+  </si>
+  <si>
+    <t>0.0791,0.5210,0.5477,0.0086</t>
+  </si>
+  <si>
+    <t>0.0258,0.8538,0.4343,0.0032</t>
+  </si>
+  <si>
+    <t>0.0005,0.9775,0.6225,0.0001</t>
+  </si>
+  <si>
+    <t>0.0151,0.9219,0.2562,0.0036</t>
+  </si>
+  <si>
+    <t>0.0026,0.9477,0.5831,0.0003</t>
+  </si>
+  <si>
+    <t>0.0084,0.0266,0.0129,0.9887</t>
+  </si>
+  <si>
+    <t>0.0025,0.0526,0.0014,0.9972</t>
+  </si>
+  <si>
+    <t>0.0032,0.0178,0.0034,0.9959</t>
+  </si>
+  <si>
+    <t>0.0021,0.0124,0.0014,0.9977</t>
+  </si>
+  <si>
+    <t>0.0012,0.0235,0.0016,0.9982</t>
+  </si>
+  <si>
+    <t>0.0030,0.0112,0.0009,0.9976</t>
+  </si>
+  <si>
+    <t>0.0044,0.9415,0.4173,0.0006</t>
+  </si>
+  <si>
+    <t>0.0037,0.8501,0.8273,0.0005</t>
+  </si>
+  <si>
+    <t>0.0281,0.7114,0.6916,0.0060</t>
+  </si>
+  <si>
+    <t>0.0084,0.8291,0.6789,0.0017</t>
+  </si>
+  <si>
+    <t>0.0031,0.8535,0.7309,0.0004</t>
+  </si>
+  <si>
+    <t>0.0101,0.8231,0.6813,0.0019</t>
+  </si>
+  <si>
+    <t>0.9813,0.0133,0.0015,0.0034</t>
+  </si>
+  <si>
+    <t>0.9775,0.0305,0.0015,0.0015</t>
+  </si>
+  <si>
+    <t>0.9525,0.0467,0.0085,0.0038</t>
+  </si>
+  <si>
+    <t>0.9855,0.0073,0.0007,0.0030</t>
+  </si>
+  <si>
+    <t>0.9690,0.0303,0.0026,0.0034</t>
+  </si>
+  <si>
+    <t>0.9736,0.0262,0.0025,0.0027</t>
+  </si>
+  <si>
+    <t>0.9834,0.0145,0.0012,0.0014</t>
+  </si>
+  <si>
+    <t>0.9699,0.0355,0.0031,0.0014</t>
+  </si>
+  <si>
+    <t>0.9891,0.0089,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.9840,0.0113,0.0024,0.0022</t>
+  </si>
+  <si>
+    <t>0.9870,0.0042,0.0004,0.0050</t>
+  </si>
+  <si>
+    <t>0.9884,0.0066,0.0008,0.0022</t>
+  </si>
+  <si>
+    <t>0.9814,0.0147,0.0023,0.0022</t>
+  </si>
+  <si>
+    <t>0.9895,0.0050,0.0004,0.0026</t>
+  </si>
+  <si>
+    <t>0.9895,0.0062,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9776,0.0158,0.0035,0.0035</t>
+  </si>
+  <si>
+    <t>0.0100,0.0034,0.9694,0.0236</t>
+  </si>
+  <si>
+    <t>0.2652,0.0930,0.6694,0.0158</t>
+  </si>
+  <si>
+    <t>0.5257,0.0950,0.3696,0.0863</t>
+  </si>
+  <si>
+    <t>0.3675,0.0106,0.7217,0.0107</t>
+  </si>
+  <si>
+    <t>0.0824,0.9371,0.0054,0.0008</t>
+  </si>
+  <si>
+    <t>0.2304,0.8450,0.0118,0.0010</t>
+  </si>
+  <si>
+    <t>0.3159,0.7818,0.0048,0.0022</t>
+  </si>
+  <si>
+    <t>0.7513,0.3844,0.0085,0.0013</t>
+  </si>
+  <si>
+    <t>0.1630,0.8838,0.0099,0.0010</t>
+  </si>
+  <si>
+    <t>0.1329,0.9201,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.6563,0.4910,0.0060,0.0022</t>
+  </si>
+  <si>
+    <t>0.6914,0.0888,0.1875,0.0439</t>
+  </si>
+  <si>
+    <t>0.4154,0.0439,0.5342,0.0666</t>
+  </si>
+  <si>
+    <t>0.6196,0.1451,0.2575,0.0314</t>
+  </si>
+  <si>
+    <t>0.4953,0.0767,0.4464,0.0409</t>
+  </si>
+  <si>
+    <t>0.0122,0.1089,0.0053,0.9870</t>
+  </si>
+  <si>
+    <t>0.0173,0.9635,0.0602,0.0044</t>
+  </si>
+  <si>
+    <t>0.0089,0.9831,0.0251,0.0012</t>
+  </si>
+  <si>
+    <t>0.1065,0.8156,0.1006,0.0575</t>
+  </si>
+  <si>
+    <t>0.0091,0.9756,0.1008,0.0013</t>
+  </si>
+  <si>
+    <t>0.0624,0.9505,0.0141,0.0003</t>
+  </si>
+  <si>
+    <t>0.8764,0.1625,0.0117,0.0050</t>
+  </si>
+  <si>
+    <t>0.7681,0.3918,0.0071,0.0014</t>
+  </si>
+  <si>
+    <t>0.8991,0.0995,0.0164,0.0056</t>
+  </si>
+  <si>
+    <t>0.7501,0.0460,0.0086,0.2133</t>
+  </si>
+  <si>
+    <t>0.9634,0.0165,0.0028,0.0109</t>
+  </si>
+  <si>
+    <t>0.9554,0.0282,0.0030,0.0078</t>
+  </si>
+  <si>
+    <t>0.9780,0.0130,0.0018,0.0050</t>
+  </si>
+  <si>
+    <t>0.9271,0.0616,0.0117,0.0050</t>
+  </si>
+  <si>
+    <t>0.9494,0.0140,0.0053,0.0206</t>
+  </si>
+  <si>
+    <t>0.9508,0.0209,0.0125,0.0109</t>
+  </si>
+  <si>
+    <t>0.0047,0.7266,0.8531,0.0009</t>
+  </si>
+  <si>
+    <t>0.0045,0.9117,0.6473,0.0006</t>
+  </si>
+  <si>
+    <t>0.0366,0.5838,0.6601,0.0058</t>
+  </si>
+  <si>
+    <t>0.0339,0.5800,0.6570,0.0032</t>
+  </si>
+  <si>
+    <t>0.1526,0.1558,0.1148,0.8166</t>
+  </si>
+  <si>
+    <t>0.3786,0.3041,0.2260,0.3032</t>
+  </si>
+  <si>
+    <t>0.6041,0.1379,0.2310,0.0582</t>
+  </si>
+  <si>
+    <t>0.5793,0.2396,0.1996,0.0867</t>
+  </si>
+  <si>
+    <t>0.0081,0.0452,0.0044,0.9922</t>
+  </si>
+  <si>
+    <t>0.0024,0.0176,0.0012,0.9976</t>
+  </si>
+  <si>
+    <t>0.0045,0.0160,0.0022,0.9958</t>
+  </si>
+  <si>
+    <t>0.0079,0.0127,0.0046,0.9933</t>
+  </si>
+  <si>
+    <t>0.0032,0.9627,0.4076,0.0004</t>
+  </si>
+  <si>
+    <t>0.9306,0.0546,0.0187,0.0115</t>
+  </si>
+  <si>
+    <t>0.4426,0.5646,0.0203,0.0359</t>
+  </si>
+  <si>
+    <t>0.9100,0.0267,0.0169,0.0402</t>
+  </si>
+  <si>
+    <t>0.9183,0.0973,0.0109,0.0028</t>
+  </si>
+  <si>
+    <t>0.9311,0.0267,0.0067,0.0288</t>
+  </si>
+  <si>
+    <t>0.1257,0.0503,0.0096,0.9252</t>
+  </si>
+  <si>
+    <t>0.9729,0.0100,0.0012,0.0108</t>
+  </si>
+  <si>
+    <t>0.0389,0.1306,0.8809,0.0701</t>
+  </si>
+  <si>
+    <t>0.3458,0.0174,0.0055,0.7683</t>
+  </si>
+  <si>
+    <t>0.8882,0.0272,0.0042,0.0696</t>
+  </si>
+  <si>
+    <t>0.5252,0.4963,0.0442,0.0152</t>
+  </si>
+  <si>
+    <t>0.6502,0.3446,0.0311,0.0298</t>
+  </si>
+  <si>
+    <t>0.6759,0.2380,0.1218,0.0324</t>
+  </si>
+  <si>
+    <t>0.1296,0.6621,0.0155,0.2923</t>
+  </si>
+  <si>
+    <t>0.8098,0.1276,0.0722,0.0083</t>
+  </si>
+  <si>
+    <t>0.6526,0.2566,0.0489,0.0845</t>
+  </si>
+  <si>
+    <t>0.9705,0.0217,0.0051,0.0049</t>
+  </si>
+  <si>
+    <t>0.9603,0.0186,0.0031,0.0115</t>
+  </si>
+  <si>
+    <t>0.9766,0.0119,0.0020,0.0069</t>
+  </si>
+  <si>
+    <t>0.9342,0.0078,0.0027,0.0482</t>
+  </si>
+  <si>
+    <t>0.9442,0.0154,0.0023,0.0281</t>
+  </si>
+  <si>
+    <t>0.9488,0.0199,0.0033,0.0259</t>
+  </si>
+  <si>
+    <t>0.9581,0.0212,0.0042,0.0124</t>
+  </si>
+  <si>
+    <t>0.9795,0.0048,0.0008,0.0103</t>
+  </si>
+  <si>
+    <t>0.3245,0.7061,0.0082,0.0149</t>
+  </si>
+  <si>
+    <t>0.8449,0.2674,0.0049,0.0015</t>
+  </si>
+  <si>
+    <t>0.8547,0.2585,0.0045,0.0012</t>
+  </si>
+  <si>
+    <t>0.8001,0.1864,0.0366,0.0097</t>
+  </si>
+  <si>
+    <t>0.9338,0.0989,0.0064,0.0018</t>
+  </si>
+  <si>
+    <t>0.9344,0.0376,0.0142,0.0127</t>
+  </si>
+  <si>
+    <t>0.9322,0.0932,0.0077,0.0014</t>
+  </si>
+  <si>
+    <t>0.8800,0.1132,0.0066,0.0178</t>
+  </si>
+  <si>
+    <t>0.0155,0.0179,0.9844,0.0013</t>
+  </si>
+  <si>
+    <t>0.9462,0.0487,0.0088,0.0042</t>
+  </si>
+  <si>
+    <t>0.1980,0.0318,0.8141,0.0112</t>
+  </si>
+  <si>
+    <t>0.0445,0.2595,0.8604,0.0045</t>
+  </si>
+  <si>
+    <t>0.1680,0.0138,0.8672,0.0039</t>
+  </si>
+  <si>
+    <t>0.0496,0.4992,0.6910,0.0071</t>
+  </si>
+  <si>
+    <t>0.1059,0.0550,0.8725,0.0138</t>
+  </si>
+  <si>
+    <t>0.0438,0.0063,0.9607,0.0063</t>
+  </si>
+  <si>
+    <t>0.0350,0.0054,0.9764,0.0008</t>
+  </si>
+  <si>
+    <t>0.5158,0.0457,0.4762,0.0336</t>
+  </si>
+  <si>
+    <t>0.5456,0.0794,0.4019,0.0173</t>
+  </si>
+  <si>
+    <t>0.4189,0.4981,0.1644,0.0269</t>
+  </si>
+  <si>
+    <t>0.3639,0.4099,0.2742,0.0137</t>
+  </si>
+  <si>
+    <t>0.2790,0.3202,0.5208,0.0482</t>
+  </si>
+  <si>
+    <t>0.5741,0.0328,0.4624,0.0040</t>
+  </si>
+  <si>
+    <t>0.6449,0.2155,0.1081,0.0617</t>
+  </si>
+  <si>
+    <t>0.2602,0.6509,0.0859,0.0573</t>
+  </si>
+  <si>
+    <t>0.9000,0.1569,0.0063,0.0016</t>
+  </si>
+  <si>
+    <t>0.8222,0.3805,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.9612,0.0518,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.9564,0.0364,0.0055,0.0072</t>
+  </si>
+  <si>
+    <t>0.9358,0.0999,0.0034,0.0014</t>
+  </si>
+  <si>
+    <t>0.3050,0.5757,0.2130,0.0638</t>
+  </si>
+  <si>
+    <t>0.6209,0.0420,0.3166,0.0339</t>
+  </si>
+  <si>
+    <t>0.5944,0.0841,0.2515,0.0979</t>
+  </si>
+  <si>
+    <t>0.3374,0.3435,0.4523,0.0341</t>
+  </si>
+  <si>
+    <t>0.5686,0.0345,0.3226,0.0885</t>
+  </si>
+  <si>
+    <t>0.2403,0.2110,0.5974,0.0907</t>
+  </si>
+  <si>
+    <t>0.0903,0.4106,0.6812,0.0320</t>
+  </si>
+  <si>
+    <t>0.0299,0.6548,0.7085,0.0088</t>
+  </si>
+  <si>
+    <t>0.1339,0.3192,0.6903,0.0233</t>
+  </si>
+  <si>
+    <t>0.0206,0.5090,0.7937,0.0048</t>
+  </si>
+  <si>
+    <t>0.9805,0.0149,0.0020,0.0026</t>
+  </si>
+  <si>
+    <t>0.9764,0.0149,0.0021,0.0059</t>
+  </si>
+  <si>
+    <t>0.9686,0.0221,0.0028,0.0056</t>
+  </si>
+  <si>
+    <t>0.9840,0.0127,0.0010,0.0023</t>
+  </si>
+  <si>
+    <t>0.9715,0.0165,0.0020,0.0066</t>
+  </si>
+  <si>
+    <t>0.9598,0.0351,0.0018,0.0070</t>
+  </si>
+  <si>
+    <t>0.9829,0.0144,0.0018,0.0019</t>
+  </si>
+  <si>
+    <t>0.9732,0.0135,0.0016,0.0072</t>
+  </si>
+  <si>
+    <t>0.1665,0.0424,0.8234,0.0132</t>
+  </si>
+  <si>
+    <t>0.3806,0.3515,0.2849,0.0052</t>
+  </si>
+  <si>
+    <t>0.7275,0.1789,0.1284,0.0355</t>
+  </si>
+  <si>
+    <t>0.0976,0.0289,0.9070,0.0028</t>
+  </si>
+  <si>
+    <t>0.0334,0.0154,0.9683,0.0026</t>
+  </si>
+  <si>
+    <t>0.0916,0.1083,0.8406,0.0073</t>
+  </si>
+  <si>
+    <t>0.0139,0.0075,0.9830,0.0029</t>
+  </si>
+  <si>
+    <t>0.1576,0.2089,0.6771,0.0116</t>
+  </si>
+  <si>
+    <t>0.0093,0.3038,0.9439,0.0017</t>
+  </si>
+  <si>
+    <t>0.0189,0.0157,0.9718,0.0051</t>
+  </si>
+  <si>
+    <t>0.4826,0.1622,0.3661,0.0991</t>
+  </si>
+  <si>
+    <t>0.5319,0.0251,0.4907,0.0244</t>
+  </si>
+  <si>
+    <t>0.5778,0.0363,0.3083,0.0770</t>
+  </si>
+  <si>
+    <t>0.2568,0.0511,0.1334,0.6634</t>
+  </si>
+  <si>
+    <t>0.9576,0.0466,0.0041,0.0039</t>
+  </si>
+  <si>
+    <t>0.9792,0.0200,0.0018,0.0031</t>
+  </si>
+  <si>
+    <t>0.9714,0.0211,0.0025,0.0055</t>
+  </si>
+  <si>
+    <t>0.9856,0.0179,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9786,0.0137,0.0017,0.0053</t>
+  </si>
+  <si>
+    <t>0.9766,0.0214,0.0028,0.0016</t>
+  </si>
+  <si>
+    <t>0.9816,0.0164,0.0008,0.0024</t>
+  </si>
+  <si>
+    <t>0.9822,0.0103,0.0021,0.0028</t>
+  </si>
+  <si>
+    <t>0.2006,0.0984,0.7379,0.0076</t>
+  </si>
+  <si>
+    <t>0.0494,0.0844,0.8946,0.0086</t>
+  </si>
+  <si>
+    <t>0.0395,0.0317,0.9544,0.0016</t>
+  </si>
+  <si>
+    <t>0.3796,0.0380,0.6336,0.0173</t>
+  </si>
+  <si>
+    <t>0.0640,0.0230,0.9341,0.0073</t>
+  </si>
+  <si>
+    <t>0.3654,0.1152,0.3393,0.3029</t>
+  </si>
+  <si>
+    <t>0.3932,0.0379,0.6013,0.0414</t>
+  </si>
+  <si>
+    <t>0.0483,0.2651,0.7952,0.0669</t>
+  </si>
+  <si>
+    <t>0.1295,0.0067,0.0076,0.9327</t>
+  </si>
+  <si>
+    <t>0.0020,0.0290,0.0023,0.9971</t>
+  </si>
+  <si>
+    <t>0.0110,0.0218,0.0035,0.9913</t>
+  </si>
+  <si>
+    <t>0.0028,0.0035,0.0021,0.9973</t>
+  </si>
+  <si>
+    <t>0.0024,0.0007,0.0008,0.9981</t>
+  </si>
+  <si>
+    <t>0.1735,0.1326,0.0207,0.8633</t>
   </si>
 </sst>
 </file>
@@ -2264,7 +2264,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
         <v>287</v>
@@ -2334,7 +2334,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>292</v>
@@ -2376,7 +2376,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
         <v>295</v>
@@ -2474,7 +2474,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
         <v>302</v>
@@ -2502,7 +2502,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D41" t="s">
         <v>304</v>
@@ -2572,7 +2572,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>309</v>
@@ -2698,7 +2698,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>318</v>
@@ -2754,7 +2754,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D59" t="s">
         <v>322</v>
@@ -2810,7 +2810,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>326</v>
@@ -2908,7 +2908,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
         <v>333</v>
@@ -2922,7 +2922,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
         <v>334</v>
@@ -2936,7 +2936,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D72" t="s">
         <v>335</v>
@@ -2992,7 +2992,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>339</v>
@@ -3090,7 +3090,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
         <v>346</v>
@@ -3426,7 +3426,7 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
         <v>370</v>
@@ -3468,7 +3468,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>373</v>
@@ -3496,7 +3496,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
         <v>375</v>
@@ -3566,7 +3566,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>380</v>
@@ -3594,7 +3594,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
         <v>382</v>
@@ -3846,7 +3846,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>400</v>
@@ -3874,7 +3874,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
         <v>402</v>
@@ -3902,7 +3902,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
         <v>404</v>
@@ -3916,7 +3916,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
         <v>405</v>
@@ -4000,7 +4000,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>411</v>
@@ -4154,7 +4154,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
         <v>422</v>
@@ -4224,7 +4224,7 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D164" t="s">
         <v>427</v>
@@ -4532,7 +4532,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>449</v>
@@ -4602,7 +4602,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
         <v>454</v>
@@ -4616,7 +4616,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
         <v>455</v>
@@ -4630,7 +4630,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
         <v>456</v>
@@ -4644,7 +4644,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>457</v>
@@ -4672,7 +4672,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
         <v>459</v>
@@ -4686,7 +4686,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D197" t="s">
         <v>460</v>
@@ -4770,7 +4770,7 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
         <v>466</v>
@@ -4798,7 +4798,7 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
         <v>468</v>
@@ -4812,7 +4812,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
         <v>469</v>
@@ -4840,7 +4840,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>471</v>
@@ -4868,7 +4868,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
         <v>473</v>
@@ -4882,7 +4882,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>474</v>
@@ -4896,7 +4896,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
         <v>475</v>
@@ -5036,7 +5036,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
         <v>485</v>
@@ -5134,7 +5134,7 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D229" t="s">
         <v>492</v>
@@ -5162,7 +5162,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D231" t="s">
         <v>494</v>
@@ -5204,7 +5204,7 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D234" t="s">
         <v>497</v>
@@ -5358,7 +5358,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>508</v>
@@ -5400,7 +5400,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
         <v>511</v>
@@ -5414,7 +5414,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>512</v>
